--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,6 +2545,44 @@
       </c>
       <c r="F56" t="n">
         <v>101.0630035400391</v>
+      </c>
+      <c r="G56" t="n">
+        <v>101.6800003051758</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.6169967651366761</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.6068024815940813</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.4748647916562111</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:19</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="n">
+        <v>100.7626190185547</v>
       </c>
     </row>
   </sheetData>
@@ -2558,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5949,6 +5987,24 @@
           <t>101.577873,101.550461,101.640404,100.865425,101.606316,101.063004</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>102.110001,102.040001,101.260002,101.739998,101.599998,101.680000</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.532128,0.489540,0.380402,0.874573,0.006318,0.616996</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.521132,0.479753,0.375668,0.859616,0.006218,0.606802</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.4748647916562111</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>101.164444,101.631264,100.902206,100.432457,101.710945,100.275215</t>
@@ -5962,6 +6018,49 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>100.163795,99.712120,99.949821,98.769012,99.633232,98.592705</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:19</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>101.593216,101.538696,101.319763,100.700569,101.112427,100.762619</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>101.334892,101.468529,100.831528,100.731056,101.091644,99.978424</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>99.967987,98.870651,98.544151,97.579948,97.830666,97.001488</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>100.253227,99.930260,99.891579,98.711060,99.308632,98.509666</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2583,44 @@
       </c>
       <c r="F57" t="n">
         <v>100.7626190185547</v>
+      </c>
+      <c r="G57" t="n">
+        <v>101.0800018310547</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.3173828124999858</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.3139916964291908</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9125639799759049</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:40</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>101.1070404052734</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6048,6 +6086,24 @@
           <t>101.593216,101.538696,101.319763,100.700569,101.112427,100.762619</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>99.790001,100.209999,100.919998,99.250000,100.940002,101.080002</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1.803215,1.328697,0.399765,1.450569,0.172425,0.317383</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1.807010,1.325913,0.396121,1.461530,0.170819,0.313992</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9125639799759049</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>101.334892,101.468529,100.831528,100.731056,101.091644,99.978424</t>
@@ -6061,6 +6117,49 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>100.253227,99.930260,99.891579,98.711060,99.308632,98.509666</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:40</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>100.868713,100.940430,100.783356,100.384796,101.039963,101.107040</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>100.427765,100.538666,100.053726,100.601013,101.145172,100.043259</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>98.647278,97.958847,97.820618,96.970123,97.258728,97.190811</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>99.243790,99.087891,99.047424,98.324249,99.093079,98.745758</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2621,44 @@
       </c>
       <c r="F58" t="n">
         <v>101.1070404052734</v>
+      </c>
+      <c r="G58" t="n">
+        <v>101.2200012207031</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1129608154297301</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1115993025760067</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.083370962185898</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:38:08</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="n">
+        <v>99.60053253173828</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6147,6 +6185,24 @@
           <t>100.868713,100.940430,100.783356,100.384796,101.039963,101.107040</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>101.309998,101.949997,103.260002,102.559998,101.489998,101.220001</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0.441285,1.009567,2.476646,2.175202,0.450035,0.112961</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.435578,0.990257,2.398456,2.120906,0.443428,0.111600</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1.083370962185898</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>100.427765,100.538666,100.053726,100.601013,101.145172,100.043259</t>
@@ -6160,6 +6216,49 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>99.243790,99.087891,99.047424,98.324249,99.093079,98.745758</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:38:08</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>100.882545,100.777878,100.165604,100.051689,100.398407,99.600533</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>100.280861,99.896484,99.959106,100.618706,100.828568,98.889549</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>98.020294,96.637329,95.881912,94.691185,94.894051,93.461594</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>98.552391,98.304405,97.783867,97.052200,97.619095,96.290894</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,44 @@
       </c>
       <c r="F59" t="n">
         <v>99.60053253173828</v>
+      </c>
+      <c r="G59" t="n">
+        <v>97.23000335693359</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2.370529174804688</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.438063450540488</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.167439156670749</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="n">
+        <v>96.11505889892578</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,6 +6284,24 @@
           <t>100.882545,100.777878,100.165604,100.051689,100.398407,99.600533</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>100.820000,99.320000,97.809998,96.830002,97.190002,97.230003</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.062545,1.457878,2.355606,3.221687,3.208405,2.370530</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.062037,1.467860,2.408349,3.327158,3.301167,2.438064</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>2.167439156670749</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>100.280861,99.896484,99.959106,100.618706,100.828568,98.889549</t>
@@ -6259,6 +6315,49 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>98.552391,98.304405,97.783867,97.052200,97.619095,96.290894</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>97.218971,96.919022,96.185501,96.420029,96.284447,96.115059</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>96.810226,96.674995,96.526421,97.073868,96.528793,95.559006</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>95.351173,94.125153,93.107361,92.446861,92.296936,91.574806</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>95.726471,95.336433,94.390610,94.221329,94.012596,93.458267</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,44 @@
       </c>
       <c r="F60" t="n">
         <v>96.11505889892578</v>
+      </c>
+      <c r="G60" t="n">
+        <v>99.38999938964844</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3.274940490722656</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3.295040256398014</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.954613776206735</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:46</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>98.63238525390625</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6345,6 +6383,24 @@
           <t>97.218971,96.919022,96.185501,96.420029,96.284447,96.115059</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>97.930000,97.019997,97.970001,98.570000,99.879997,99.389999</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.711029,0.100975,1.784500,2.149971,3.595550,3.274940</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.726059,0.104076,1.821476,2.181161,3.599870,3.295040</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>1.954613776206735</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>96.810226,96.674995,96.526421,97.073868,96.528793,95.559006</t>
@@ -6358,6 +6414,49 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>95.726471,95.336433,94.390610,94.221329,94.012596,93.458267</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:46</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>99.122536,99.315575,99.359444,99.054100,98.847855,98.632385</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>99.164963,99.379173,98.918289,99.363220,98.737488,98.029617</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>97.088905,96.614136,96.676552,95.731331,95.519226,95.309486</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>97.612770,97.659889,97.626877,97.223450,96.929718,96.579063</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +2735,44 @@
       </c>
       <c r="F61" t="n">
         <v>98.63238525390625</v>
+      </c>
+      <c r="G61" t="n">
+        <v>105.0400009155273</v>
+      </c>
+      <c r="H61" t="n">
+        <v>6.407615661621094</v>
+      </c>
+      <c r="I61" t="n">
+        <v>6.100167179905174</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3.037531282034071</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:24:03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" t="n">
+        <v>104.6136703491211</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +2786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6444,6 +6482,24 @@
           <t>99.122536,99.315575,99.359444,99.054100,98.847855,98.632385</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>100.019997,101.199997,100.900002,101.540001,104.480003,105.040001</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.897461,1.884422,1.540558,2.485901,5.632148,6.407616</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.897281,1.862077,1.526816,2.448199,5.390647,6.100167</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>3.037531282034071</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>99.164963,99.379173,98.918289,99.363220,98.737488,98.029617</t>
@@ -6457,6 +6513,49 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>97.612770,97.659889,97.626877,97.223450,96.929718,96.579063</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:24:03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>104.852394,104.820885,105.048370,105.136497,105.082695,104.613670</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>104.660179,104.524536,104.515976,104.906372,104.739754,103.988327</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>102.920731,102.105919,101.894279,101.316635,100.953979,100.178635</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>103.478539,103.113159,102.995026,102.809380,102.441322,101.640678</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,6 +2773,44 @@
       </c>
       <c r="F62" t="n">
         <v>104.6136703491211</v>
+      </c>
+      <c r="G62" t="n">
+        <v>113.1900024414062</v>
+      </c>
+      <c r="H62" t="n">
+        <v>8.576332092285156</v>
+      </c>
+      <c r="I62" t="n">
+        <v>7.576934276262399</v>
+      </c>
+      <c r="J62" t="n">
+        <v>6.00135865443035</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:55</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="n">
+        <v>111.3260116577148</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6581,24 @@
           <t>104.852394,104.820885,105.048370,105.136497,105.082695,104.613670</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>105.639999,111.129997,114.330002,112.699997,113.209999,113.190002</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.787605,6.309112,9.281632,7.563500,8.127304,8.576332</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.745556,5.677236,8.118282,6.711180,7.178963,7.576935</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>6.00135865443035</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>104.660179,104.524536,104.515976,104.906372,104.739754,103.988327</t>
@@ -6556,6 +6612,49 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>103.478539,103.113159,102.995026,102.809380,102.441322,101.640678</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:55</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>113.395721,112.752693,112.397728,111.920738,111.643143,111.326012</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>112.858757,112.256844,112.011284,111.556770,110.898361,110.668007</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>111.067459,109.530106,108.288200,106.833916,105.976501,105.036064</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>111.985237,110.805092,109.842712,109.018692,108.183228,107.436317</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2811,6 +2811,44 @@
       </c>
       <c r="F63" t="n">
         <v>111.3260116577148</v>
+      </c>
+      <c r="G63" t="n">
+        <v>109.0999984741211</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.226013183593707</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2.040342084992536</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.493976394779987</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:40:02</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>107.2031707763672</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6642,6 +6680,24 @@
           <t>113.395721,112.752693,112.397728,111.920738,111.643143,111.326012</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>111.849998,111.589996,111.139999,111.019997,108.860001,109.099998</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1.545723,1.162697,1.257729,0.900741,2.783142,2.226014</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1.381960,1.041936,1.131662,0.811333,2.556625,2.040342</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1.493976394779987</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>112.858757,112.256844,112.011284,111.556770,110.898361,110.668007</t>
@@ -6655,6 +6711,49 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>111.985237,110.805092,109.842712,109.018692,108.183228,107.436317</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:40:02</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>108.861694,108.445984,108.113922,107.798996,107.497009,107.203171</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>108.520615,108.168411,107.964691,107.516266,107.118973,106.873688</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>106.881744,105.913879,104.984055,104.128860,103.436584,102.743790</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>107.689484,106.882553,106.123901,105.581436,104.959671,104.445663</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2849,6 +2849,44 @@
       </c>
       <c r="F64" t="n">
         <v>107.2031707763672</v>
+      </c>
+      <c r="G64" t="n">
+        <v>111.4100036621094</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4.206832885742173</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3.775992054089592</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.200281868853538</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:52</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>110.2998352050781</v>
       </c>
     </row>
   </sheetData>
@@ -2862,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6741,6 +6779,24 @@
           <t>108.861694,108.445984,108.113922,107.798996,107.497009,107.203171</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>108.410004,108.779999,110.419998,111.139999,111.519997,111.410004</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.451690,0.334015,2.306076,3.341003,4.022988,4.206833</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.416650,0.307055,2.088459,3.006121,3.607414,3.775992</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>2.200281868853538</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>108.520615,108.168411,107.964691,107.516266,107.118973,106.873688</t>
@@ -6754,6 +6810,49 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>107.689484,106.882553,106.123901,105.581436,104.959671,104.445663</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:52</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>111.570862,111.337936,111.062515,110.807709,110.507812,110.299835</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>111.095200,110.757370,110.708923,110.438904,109.760986,109.660934</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>109.668259,108.793961,107.929520,107.134949,106.352432,105.804276</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>110.508011,109.810471,109.123428,108.665176,108.021622,107.582932</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,44 @@
       </c>
       <c r="F65" t="n">
         <v>110.2998352050781</v>
+      </c>
+      <c r="G65" t="n">
+        <v>116.5699996948242</v>
+      </c>
+      <c r="H65" t="n">
+        <v>6.270164489746122</v>
+      </c>
+      <c r="I65" t="n">
+        <v>5.37888350875969</v>
+      </c>
+      <c r="J65" t="n">
+        <v>5.623281689170568</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:54</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" t="n">
+        <v>115.0453033447266</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6840,6 +6878,24 @@
           <t>111.570862,111.337936,111.062515,110.807709,110.507812,110.299835</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>116.769997,117.919998,118.339996,118.900002,116.779999,116.570000</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>5.199135,6.582062,7.277481,8.092293,6.272187,6.270165</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4.452458,5.581803,6.149638,6.805965,5.370943,5.378884</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>5.623281689170568</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>111.095200,110.757370,110.708923,110.438904,109.760986,109.660934</t>
@@ -6853,6 +6909,49 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>110.508011,109.810471,109.123428,108.665176,108.021622,107.582932</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:54</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>116.284721,115.923767,115.722054,115.515762,115.327843,115.045303</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>115.916603,115.570648,115.287521,115.005707,114.738617,114.529213</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>114.079384,112.940147,112.036568,111.150841,110.229599,109.594833</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>115.079781,114.157310,113.443199,112.926849,112.233513,111.682930</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,44 @@
       </c>
       <c r="F66" t="n">
         <v>115.0453033447266</v>
+      </c>
+      <c r="G66" t="n">
+        <v>119.4400024414062</v>
+      </c>
+      <c r="H66" t="n">
+        <v>4.394699096679645</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3.679419798099515</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2.276308750719474</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:14</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>119.3915100097656</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6939,6 +6977,24 @@
           <t>116.284721,115.923767,115.722054,115.515762,115.327843,115.045303</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>117.309998,117.370003,118.220001,118.559998,119.129997,119.440002</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1.025277,1.446236,2.497947,3.044236,3.802154,4.394699</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.873989,1.232202,2.112965,2.567675,3.191601,3.679420</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>2.276308750719474</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>115.916603,115.570648,115.287521,115.005707,114.738617,114.529213</t>
@@ -6952,6 +7008,49 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>115.079781,114.157310,113.443199,112.926849,112.233513,111.682930</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:14</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>119.719200,119.685783,119.612366,119.501595,119.381920,119.391510</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>119.413071,119.428993,119.315086,119.126350,118.611938,118.585579</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>118.063011,117.401337,116.674728,115.944817,115.132149,114.779907</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>118.917328,118.503807,117.987259,117.606285,117.129517,116.749397</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2963,6 +2963,44 @@
       </c>
       <c r="F67" t="n">
         <v>119.3915100097656</v>
+      </c>
+      <c r="G67" t="n">
+        <v>114.7600021362305</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4.631507873535128</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4.035820658174187</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.991506295153239</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:29</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="n">
+        <v>113.9004516601562</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,6 +7076,24 @@
           <t>119.719200,119.685783,119.612366,119.501595,119.381920,119.391510</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>117.080002,113.870003,114.510002,114.900002,114.690002,114.760002</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2.639198,5.815780,5.102364,4.601593,4.691918,4.631508</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2.254184,5.107386,4.455824,4.004868,4.090956,4.035821</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>3.991506295153239</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>119.413071,119.428993,119.315086,119.126350,118.611938,118.585579</t>
@@ -7051,6 +7107,49 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>118.917328,118.503807,117.987259,117.606285,117.129517,116.749397</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:29</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>114.623779,114.376221,114.228836,114.136124,114.007080,113.900452</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>114.331970,114.246002,113.946960,113.845505,113.515228,113.573425</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>112.558807,111.730896,110.922165,110.273514,109.568985,109.042572</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>113.408386,112.771439,112.129456,111.802902,111.322388,110.919006</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,6 +3001,44 @@
       </c>
       <c r="F68" t="n">
         <v>113.9004516601562</v>
+      </c>
+      <c r="G68" t="n">
+        <v>116.9599990844727</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3.059547424316463</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2.61589214113002</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2.147518916153924</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:47</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F69" t="n">
+        <v>116.454475402832</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7137,6 +7175,24 @@
           <t>114.623779,114.376221,114.228836,114.136124,114.007080,113.900452</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>113.330002,116.260002,117.290001,117.019997,116.849998,116.959999</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1.293777,1.883781,3.061165,2.883873,2.842918,3.059547</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1.141602,1.620317,2.609911,2.464427,2.432964,2.615892</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>2.147518916153924</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>114.331970,114.246002,113.946960,113.845505,113.515228,113.573425</t>
@@ -7150,6 +7206,49 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>113.408386,112.771439,112.129456,111.802902,111.322388,110.919006</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:47</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>116.883812,116.806358,116.639801,116.655457,116.430702,116.454475</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>116.521423,116.777908,116.456558,116.465797,115.935074,116.003296</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>115.261200,114.700211,114.008934,113.547882,112.886658,112.383698</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>115.945053,115.604469,115.045105,114.881554,114.306328,114.000023</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3039,6 +3039,44 @@
       </c>
       <c r="F69" t="n">
         <v>116.454475402832</v>
+      </c>
+      <c r="G69" t="n">
+        <v>120.5299987792969</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4.075523376464872</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3.381335283946683</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.602113579286785</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:36</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>120.3759841918945</v>
       </c>
     </row>
   </sheetData>
@@ -3052,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7236,6 +7274,24 @@
           <t>116.883812,116.806358,116.639801,116.655457,116.430702,116.454475</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>120.809998,120.080002,121.849998,122.150002,120.629997,120.529999</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>3.926186,3.273644,5.210197,5.494545,4.199295,4.075524</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3.249885,2.726219,4.275911,4.498194,3.481137,3.381336</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>3.602113579286785</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>116.521423,116.777908,116.456558,116.465797,115.935074,116.003296</t>
@@ -7249,6 +7305,49 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>115.945053,115.604469,115.045105,114.881554,114.306328,114.000023</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:36</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>120.218292,120.296860,120.133415,120.358353,120.176811,120.375984</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>120.074043,120.136909,119.850082,120.183754,119.655891,119.794365</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>118.416939,117.875366,117.170647,116.822800,116.101440,115.806923</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>119.072624,118.845818,118.253151,118.206306,117.701569,117.420601</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,44 @@
       </c>
       <c r="F70" t="n">
         <v>120.3759841918945</v>
+      </c>
+      <c r="G70" t="n">
+        <v>120.2200012207031</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.1559829711913778</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.1297479367888377</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.71036249886414</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:35</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" t="n">
+        <v>119.8942565917969</v>
       </c>
     </row>
   </sheetData>
@@ -3090,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,6 +7373,24 @@
           <t>120.218292,120.296860,120.133415,120.358353,120.176811,120.375984</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>121.260002,121.860001,121.120003,121.379997,120.580002,120.220001</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1.041710,1.563141,0.986588,1.021644,0.403191,0.155983</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.859072,1.282735,0.814554,0.841691,0.334376,0.129748</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.71036249886414</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>120.074043,120.136909,119.850082,120.183754,119.655891,119.794365</t>
@@ -7348,6 +7404,49 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>119.072624,118.845818,118.253151,118.206306,117.701569,117.420601</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:35</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>120.230988,119.821442,119.767075,120.084381,119.898422,119.894257</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>119.956444,119.665688,119.571762,119.855713,119.730194,119.431168</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>118.440430,117.501091,116.792076,116.682465,115.982712,115.502342</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>119.134583,118.434708,118.012436,118.035416,117.548256,117.052139</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3115,6 +3115,44 @@
       </c>
       <c r="F71" t="n">
         <v>119.8942565917969</v>
+      </c>
+      <c r="G71" t="n">
+        <v>119.7099990844727</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.1842575073242472</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.1539198970290084</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1.493822816895461</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:21</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>119.9320907592773</v>
       </c>
     </row>
   </sheetData>
@@ -3128,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,6 +7472,24 @@
           <t>120.230988,119.821442,119.767075,120.084381,119.898422,119.894257</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>123.900002,121.750000,123.019997,121.980003,119.820000,119.709999</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>3.669014,1.928558,3.252922,1.895622,0.078422,0.184258</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2.961270,1.584031,2.644222,1.554044,0.065450,0.153920</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>1.493822816895461</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>119.956444,119.665688,119.571762,119.855713,119.730194,119.431168</t>
@@ -7447,6 +7503,49 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>119.134583,118.434708,118.012436,118.035416,117.548256,117.052139</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:21</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>119.716713,119.504951,119.524124,119.755539,119.829628,119.932091</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>119.634529,119.348373,119.418961,119.733788,119.711205,119.670036</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>117.605400,116.800285,116.236557,115.975517,115.563797,115.210732</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>118.418724,117.776939,117.416084,117.481880,117.142052,116.859520</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3153,6 +3153,44 @@
       </c>
       <c r="F72" t="n">
         <v>119.9320907592773</v>
+      </c>
+      <c r="G72" t="n">
+        <v>118.0500030517578</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.882087707519489</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.59431398463777</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1.108060486080185</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:29:04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>117.9751510620117</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7533,6 +7571,24 @@
           <t>119.716713,119.504951,119.524124,119.755539,119.829628,119.932091</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>118.690002,118.709999,118.320000,118.820000,117.809998,118.050003</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1.026711,0.794952,1.204124,0.935539,2.019630,1.882088</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.865035,0.669659,1.017685,0.787358,1.714312,1.594314</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>1.108060486080185</v>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>119.634529,119.348373,119.418961,119.733788,119.711205,119.670036</t>
@@ -7546,6 +7602,49 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>118.418724,117.776939,117.416084,117.481880,117.142052,116.859520</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:29:04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>118.042709,118.009209,118.240929,118.177147,118.004372,117.975151</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>117.842026,118.108124,118.069504,118.022850,117.797935,117.958572</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>116.844406,116.145256,115.615089,114.987930,114.075432,113.686630</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>117.253174,116.806602,116.398125,116.088905,115.371307,115.075630</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,6 +3191,44 @@
       </c>
       <c r="F73" t="n">
         <v>117.9751510620117</v>
+      </c>
+      <c r="G73" t="n">
+        <v>118.4599990844727</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.4848480224609517</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.4092926103394711</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.7386470276019838</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:38</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="n">
+        <v>118.3780746459961</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7632,6 +7670,24 @@
           <t>118.042709,118.009209,118.240929,118.177147,118.004372,117.975151</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>120.120003,118.190002,118.779999,119.080002,119.110001,118.459999</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2.077294,0.180793,0.539070,0.902855,1.105629,0.484848</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1.729349,0.152968,0.453839,0.758192,0.928242,0.409293</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.7386470276019838</v>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>117.842026,118.108124,118.069504,118.022850,117.797935,117.958572</t>
@@ -7645,6 +7701,49 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>117.253174,116.806602,116.398125,116.088905,115.371307,115.075630</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:38</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>118.420151,118.203629,118.368607,118.485222,118.437904,118.378075</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>118.159096,118.414604,118.099571,118.318420,118.175835,118.451004</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>117.305840,116.551651,116.105988,115.754738,115.230316,114.697891</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>117.703568,117.139542,116.896362,116.792694,116.291321,115.905510</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,44 @@
       </c>
       <c r="F74" t="n">
         <v>118.3780746459961</v>
+      </c>
+      <c r="G74" t="n">
+        <v>119.1500015258789</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.7719268798828125</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.6478614099850877</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.651143533373661</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:49</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>119.4575958251953</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,6 +7769,24 @@
           <t>118.420151,118.203629,118.368607,118.485222,118.437904,118.378075</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>119.459999,119.260002,117.180000,118.059998,118.589996,119.150002</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1.039848,1.056373,1.188607,0.425224,0.152092,0.771927</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.870457,0.885773,1.014343,0.360177,0.128251,0.647861</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.651143533373661</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>118.159096,118.414604,118.099571,118.318420,118.175835,118.451004</t>
@@ -7744,6 +7800,49 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>117.703568,117.139542,116.896362,116.792694,116.291321,115.905510</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:49</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>119.220673,119.194717,119.322159,119.467453,119.524704,119.457596</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>119.144043,119.281418,118.901764,119.303818,119.309097,119.337311</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>117.632294,117.018066,116.555145,116.251251,115.754135,115.291885</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>118.169449,117.806244,117.505554,117.487640,117.056396,116.755814</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3267,44 @@
       </c>
       <c r="F75" t="n">
         <v>119.4575958251953</v>
+      </c>
+      <c r="G75" t="n">
+        <v>122.879997253418</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3.42240142822267</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2.785157474543705</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1.456128778935476</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" t="n">
+        <v>123.6503753662109</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7830,6 +7868,24 @@
           <t>119.220673,119.194717,119.322159,119.467453,119.524704,119.457596</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>117.919998,117.320000,118.190002,118.379997,121.190002,122.879997</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.300675,1.874717,1.132157,1.087456,1.665298,3.422401</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1.103015,1.597952,0.957912,0.918614,1.374122,2.785157</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>1.456128778935476</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>119.144043,119.281418,118.901764,119.303818,119.309097,119.337311</t>
@@ -7843,6 +7899,49 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>118.169449,117.806244,117.505554,117.487640,117.056396,116.755814</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>122.505920,122.678108,122.782349,123.068001,123.117386,123.650375</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>122.490089,122.586090,122.740784,123.119812,122.909180,123.480927</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>120.022781,119.861412,119.718666,119.625526,119.352959,119.575989</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>120.833260,120.913010,120.772034,120.931046,120.775307,120.995499</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3305,6 +3305,44 @@
       </c>
       <c r="F76" t="n">
         <v>123.6503753662109</v>
+      </c>
+      <c r="G76" t="n">
+        <v>119.0899963378906</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4.56037902832027</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3.829355251117178</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2.94784341566304</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:14</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="n">
+        <v>119.3806304931641</v>
       </c>
     </row>
   </sheetData>
@@ -3318,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7929,6 +7967,24 @@
           <t>122.505920,122.678108,122.782349,123.068001,123.117386,123.650375</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>121.800003,119.949997,117.949997,118.580002,119.389999,119.089996</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.705917,2.728111,4.832352,4.487999,3.727387,4.560379</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0.579571,2.274374,4.096950,3.784786,3.122026,3.829355</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>2.94784341566304</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>122.490089,122.586090,122.740784,123.119812,122.909180,123.480927</t>
@@ -7942,6 +7998,49 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>120.833260,120.913010,120.772034,120.931046,120.775307,120.995499</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:14</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>118.960144,119.022034,119.096420,119.214828,119.258163,119.380630</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>119.087448,119.101044,118.980438,119.151245,119.114334,119.353073</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>116.860855,116.698013,116.466476,116.489609,116.257050,116.135742</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>117.601883,117.501526,117.348404,117.420685,117.365967,117.311462</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,6 +3343,44 @@
       </c>
       <c r="F77" t="n">
         <v>119.3806304931641</v>
+      </c>
+      <c r="G77" t="n">
+        <v>120.7399978637695</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.359367370605426</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.125863338294237</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.681429369822013</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:36</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" t="n">
+        <v>120.8338851928711</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8028,6 +8066,24 @@
           <t>118.960144,119.022034,119.096420,119.214828,119.258163,119.380630</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>119.300003,119.680000,119.779999,119.589996,120.760002,120.739998</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0.339859,0.657966,0.683579,0.375168,1.501839,1.359368</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0.284878,0.549771,0.570695,0.313712,1.243656,1.125864</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.681429369822013</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>119.087448,119.101044,118.980438,119.151245,119.114334,119.353073</t>
@@ -8041,6 +8097,49 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>117.601883,117.501526,117.348404,117.420685,117.365967,117.311462</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:36</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>120.616089,120.639732,120.704201,120.709831,120.873146,120.833885</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>120.687943,120.800278,120.507210,120.462982,120.541435,120.717339</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>118.857246,118.588226,118.428581,118.332733,118.145439,117.876320</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>119.477730,119.349686,119.201706,119.198265,119.118248,119.058968</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,6 +3381,44 @@
       </c>
       <c r="F78" t="n">
         <v>120.8338851928711</v>
+      </c>
+      <c r="G78" t="n">
+        <v>120.1900024414062</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.6438827514648438</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.5357207241748269</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.530922536643295</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:22</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>120.2695770263672</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8127,6 +8165,24 @@
           <t>120.616089,120.639732,120.704201,120.709831,120.873146,120.833885</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>121.220001,121.540001,121.080002,121.570000,120.400002,120.190002</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0.603912,0.900269,0.375801,0.860169,0.473144,0.643883</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.498195,0.740718,0.310374,0.707550,0.392977,0.535721</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.530922536643295</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>120.687943,120.800278,120.507210,120.462982,120.541435,120.717339</t>
@@ -8140,6 +8196,49 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>119.477730,119.349686,119.201706,119.198265,119.118248,119.058968</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:22</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>120.172112,120.064392,120.104942,120.214905,120.264565,120.269577</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>120.178963,120.407303,119.986946,120.000893,120.147034,120.049629</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>118.400780,117.951851,117.619194,117.636345,117.272560,117.104340</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>119.054420,118.766235,118.530403,118.580910,118.421143,118.347359</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +3419,44 @@
       </c>
       <c r="F79" t="n">
         <v>120.2695770263672</v>
+      </c>
+      <c r="G79" t="n">
+        <v>119.5100021362305</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.759574890136733</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.6355743256291528</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.4369136326023306</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:29</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="n">
+        <v>119.427001953125</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8226,6 +8264,24 @@
           <t>120.172112,120.064392,120.104942,120.214905,120.264565,120.269577</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>120.809998,119.320000,120.269997,120.769997,119.980003,119.510002</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0.637886,0.744392,0.165055,0.555092,0.284562,0.759575</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0.528007,0.623862,0.137237,0.459627,0.237174,0.635574</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.4369136326023306</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>120.178963,120.407303,119.986946,120.000893,120.147034,120.049629</t>
@@ -8239,6 +8295,49 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>119.054420,118.766235,118.530403,118.580910,118.421143,118.347359</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:29</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>119.583138,119.480278,119.471306,119.354660,119.384422,119.427002</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>119.550316,119.687996,119.630745,119.193329,119.432152,119.059319</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>117.761879,117.420341,116.948166,116.600258,116.251419,116.189880</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>118.370453,118.204765,117.942078,117.657288,117.516418,117.335579</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,44 @@
       </c>
       <c r="F80" t="n">
         <v>119.427001953125</v>
+      </c>
+      <c r="G80" t="n">
+        <v>118.5500030517578</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.8769989013671875</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.7397713022278861</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.8955517547955464</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:42</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" t="n">
+        <v>119.2167816162109</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8325,6 +8363,24 @@
           <t>119.583138,119.480278,119.471306,119.354660,119.384422,119.427002</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>120.320000,120.489998,120.790001,120.690002,118.220001,118.550003</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.736862,1.009720,1.318695,1.335342,1.164421,0.876999</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.612418,0.838011,1.091725,1.106423,0.984961,0.739771</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.8955517547955464</v>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>119.550316,119.687996,119.630745,119.193329,119.432152,119.059319</t>
@@ -8338,6 +8394,49 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>118.370453,118.204765,117.942078,117.657288,117.516418,117.335579</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:42</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>119.192566,119.135498,119.161774,119.061798,119.162491,119.216782</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>119.169449,119.276520,119.178329,118.810593,119.095291,118.960083</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>117.238510,117.054626,116.866867,116.660126,116.572281,116.543976</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>117.893936,117.756561,117.723694,117.597290,117.520935,117.553864</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3495,44 @@
       </c>
       <c r="F81" t="n">
         <v>119.2167816162109</v>
+      </c>
+      <c r="G81" t="n">
+        <v>115.3099975585938</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.906784057617145</v>
+      </c>
+      <c r="I81" t="n">
+        <v>3.38807054057212</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2.564333129506772</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:55</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" t="n">
+        <v>114.4622802734375</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,6 +8462,24 @@
           <t>119.192566,119.135498,119.161774,119.061798,119.162491,119.216782</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>117.320000,116.720001,115.820000,116.250000,115.660004,115.309998</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1.872566,2.415497,3.341774,2.811798,3.502487,3.906784</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1.596119,2.069480,2.885317,2.418751,3.028261,3.388071</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>2.564333129506772</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>119.169449,119.276520,119.178329,118.810593,119.095291,118.960083</t>
@@ -8437,6 +8493,49 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>117.893936,117.756561,117.723694,117.597290,117.520935,117.553864</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:55</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>115.204346,115.119255,114.847511,114.626846,114.624901,114.462280</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>115.244812,115.410652,114.750534,114.418747,114.564331,114.331261</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>113.292130,112.861176,112.406631,111.964638,111.648819,111.308311</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>113.941528,113.694992,113.365265,112.960892,112.859352,112.471771</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,6 +3533,44 @@
       </c>
       <c r="F82" t="n">
         <v>114.4622802734375</v>
+      </c>
+      <c r="G82" t="n">
+        <v>110.2799987792969</v>
+      </c>
+      <c r="H82" t="n">
+        <v>4.182281494140625</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3.792420693176299</v>
+      </c>
+      <c r="J82" t="n">
+        <v>4.272350699757612</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:59</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" t="n">
+        <v>109.6928558349609</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8523,6 +8561,24 @@
           <t>115.204346,115.119255,114.847511,114.626846,114.624901,114.462280</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>113.070000,108.470001,109.080002,109.540001,110.330002,110.279999</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2.134346,6.649254,5.767509,5.086845,4.294899,4.182281</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1.887633,6.130039,5.287412,4.643824,3.892775,3.792420</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>4.272350699757612</v>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>115.244812,115.410652,114.750534,114.418747,114.564331,114.331261</t>
@@ -8536,6 +8592,49 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>113.941528,113.694992,113.365265,112.960892,112.859352,112.471771</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:59</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>110.010941,110.128510,109.926239,109.945801,109.938675,109.692856</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>109.984711,110.344177,109.713562,110.129517,110.080978,109.790466</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>107.412750,107.028809,106.380402,105.938095,105.610123,104.927643</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>108.410583,108.230850,107.687515,107.397385,107.244614,106.715393</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,6 +3571,44 @@
       </c>
       <c r="F83" t="n">
         <v>109.6928558349609</v>
+      </c>
+      <c r="G83" t="n">
+        <v>110.0299987792969</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.3371429443359801</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.3064100227904543</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.7342431386572968</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:22</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="n">
+        <v>109.0837249755859</v>
       </c>
     </row>
   </sheetData>
@@ -3584,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8660,24 @@
           <t>110.010941,110.128510,109.926239,109.945801,109.938675,109.692856</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>111.220001,109.639999,108.379997,109.040001,109.599998,110.029999</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1.209060,0.488511,1.546242,0.905800,0.338677,0.337143</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1.087089,0.445559,1.426686,0.830704,0.309011,0.306410</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.7342431386572968</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>109.984711,110.344177,109.713562,110.129517,110.080978,109.790466</t>
@@ -8635,6 +8691,49 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>108.410583,108.230850,107.687515,107.397385,107.244614,106.715393</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:22</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>109.889954,110.084976,109.790100,109.538330,109.451462,109.083725</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>109.875397,110.366684,109.738052,109.587357,109.437164,109.119171</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>107.719574,107.342026,106.557968,105.870941,105.396942,104.699875</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>108.464615,108.409668,107.754730,107.190720,106.810913,106.405579</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,6 +3609,44 @@
       </c>
       <c r="F84" t="n">
         <v>109.0837249755859</v>
+      </c>
+      <c r="G84" t="n">
+        <v>109.5899963378906</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.5062713623047301</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.4619685913153803</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3495995791088116</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:31</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="n">
+        <v>109.3058395385742</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8721,6 +8759,24 @@
           <t>109.889954,110.084976,109.790100,109.538330,109.451462,109.083725</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>109.769997,110.370003,110.339996,109.980003,109.050003,109.589996</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0.119957,0.285027,0.549896,0.441673,0.401459,0.506271</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.109281,0.258247,0.498365,0.401594,0.368142,0.461969</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3495995791088116</v>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>109.875397,110.366684,109.738052,109.587357,109.437164,109.119171</t>
@@ -8734,6 +8790,49 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>108.464615,108.409668,107.754730,107.190720,106.810913,106.405579</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:31</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>109.525620,109.606667,109.459457,109.441231,109.484520,109.305840</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>109.571526,109.861946,109.187782,109.519302,109.645050,109.338524</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>107.915062,107.585037,107.048759,106.802567,106.527107,106.084564</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>108.554016,108.394333,107.946609,107.700867,107.579704,107.405937</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,6 +3647,44 @@
       </c>
       <c r="F85" t="n">
         <v>109.3058395385742</v>
+      </c>
+      <c r="G85" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3.194160461425795</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2.839253743489596</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1.651907602216678</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:41</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="n">
+        <v>111.6572341918945</v>
       </c>
     </row>
   </sheetData>
@@ -3660,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8820,6 +8858,24 @@
           <t>109.525620,109.606667,109.459457,109.441231,109.484520,109.305840</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>109.489998,111.830002,111.239998,111.209999,111.559998,112.500000</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0.035622,2.223335,1.780541,1.768768,2.075478,3.194160</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.032535,1.988138,1.600630,1.590476,1.860414,2.839253</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1.651907602216678</v>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>109.571526,109.861946,109.187782,109.519302,109.645050,109.338524</t>
@@ -8833,6 +8889,49 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>108.554016,108.394333,107.946609,107.700867,107.579704,107.405937</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:41</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>112.575386,112.571922,112.385674,112.187996,111.967293,111.657234</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>112.587105,112.463287,112.334633,111.933128,111.896233,111.538658</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>110.443405,109.762077,109.073143,108.634270,108.235626,107.725952</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>111.244560,110.854164,110.265144,109.873222,109.550148,109.280228</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,6 +3685,44 @@
       </c>
       <c r="F86" t="n">
         <v>111.6572341918945</v>
+      </c>
+      <c r="G86" t="n">
+        <v>108.5699996948242</v>
+      </c>
+      <c r="H86" t="n">
+        <v>3.087234497070284</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2.843542880858513</v>
+      </c>
+      <c r="J86" t="n">
+        <v>3.703108214797185</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:55</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6</v>
+      </c>
+      <c r="F87" t="n">
+        <v>108.3630218505859</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8919,6 +8957,24 @@
           <t>112.575386,112.571922,112.385674,112.187996,111.967293,111.657234</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>110.910004,108.779999,108.190002,105.629997,107.349998,108.570000</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1.665382,3.791923,4.195672,6.557999,4.617295,3.087234</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1.501562,3.485864,3.878058,6.208462,4.301159,2.843543</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>3.703108214797185</v>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>112.587105,112.463287,112.334633,111.933128,111.896233,111.538658</t>
@@ -8932,6 +8988,49 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>111.244560,110.854164,110.265144,109.873222,109.550148,109.280228</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:55</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>108.474907,108.446915,108.377670,108.350563,108.197525,108.363022</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>108.428802,108.506126,108.400421,108.457352,108.419815,108.360008</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>106.209999,105.560623,105.004921,104.545708,104.208435,103.971130</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>107.042725,106.710564,106.239288,105.939285,105.600876,105.717224</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,6 +3723,44 @@
       </c>
       <c r="F87" t="n">
         <v>108.3630218505859</v>
+      </c>
+      <c r="G87" t="n">
+        <v>108.129997253418</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.2330245971679261</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.2155041182714543</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1.0785500941396</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:33</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" t="n">
+        <v>108.4835510253906</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +9056,24 @@
           <t>108.474907,108.446915,108.377670,108.350563,108.197525,108.363022</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>106.050003,107.260002,107.400002,106.730003,107.730003,108.129997</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2.424904,1.186913,0.977668,1.620560,0.467522,0.233025</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2.286567,1.106575,0.910306,1.518373,0.433975,0.215504</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>1.0785500941396</v>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>108.428802,108.506126,108.400421,108.457352,108.419815,108.360008</t>
@@ -9031,6 +9087,49 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>107.042725,106.710564,106.239288,105.939285,105.600876,105.717224</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:33</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>107.939987,108.187149,108.377029,108.363785,108.446609,108.483551</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>108.042206,108.266953,108.504593,108.675018,108.797379,108.755707</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>106.058807,105.662735,105.319824,104.869720,104.834366,104.520798</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>106.793945,106.736465,106.492111,106.294113,106.084427,106.008881</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3761,6 +3761,44 @@
       </c>
       <c r="F88" t="n">
         <v>108.4835510253906</v>
+      </c>
+      <c r="G88" t="n">
+        <v>102.7699966430664</v>
+      </c>
+      <c r="H88" t="n">
+        <v>5.71355438232419</v>
+      </c>
+      <c r="I88" t="n">
+        <v>5.559554898272605</v>
+      </c>
+      <c r="J88" t="n">
+        <v>4.124876596571431</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:19:10</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" t="n">
+        <v>102.746337890625</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9117,6 +9155,24 @@
           <t>107.939987,108.187149,108.377029,108.363785,108.446609,108.483551</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>107.070000,103.750000,104.080002,104.160004,102.370003,102.769997</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0.869987,4.437149,4.297027,4.203781,6.076606,5.713554</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.812541,4.276770,4.128581,4.035888,5.935925,5.559555</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>4.124876596571431</v>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>108.042206,108.266953,108.504593,108.675018,108.797379,108.755707</t>
@@ -9130,6 +9186,49 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>106.793945,106.736465,106.492111,106.294113,106.084427,106.008881</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:19:10</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>102.849686,102.865433,102.727585,102.898605,102.804092,102.746338</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>102.939651,103.136963,102.989044,103.270065,103.484985,103.185654</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>100.462585,99.766037,99.113937,98.711792,98.544479,98.017990</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>101.409058,101.151947,100.555817,100.488953,100.145294,99.841705</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,6 +3799,44 @@
       </c>
       <c r="F89" t="n">
         <v>102.746337890625</v>
+      </c>
+      <c r="G89" t="n">
+        <v>105.129997253418</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.383659362792969</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2.267344644789736</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.256941717607761</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:43</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" t="n">
+        <v>104.710563659668</v>
       </c>
     </row>
   </sheetData>
@@ -3812,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9216,6 +9254,24 @@
           <t>102.849686,102.865433,102.727585,102.898605,102.804092,102.746338</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>102.070000,105.989998,105.940002,105.269997,105.199997,105.129997</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0.779686,3.124565,3.212417,2.371392,2.395905,2.383659</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0.763874,2.947981,3.032299,2.252676,2.277476,2.267345</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>2.256941717607761</v>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>102.939651,103.136963,102.989044,103.270065,103.484985,103.185654</t>
@@ -9229,6 +9285,49 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>101.409058,101.151947,100.555817,100.488953,100.145294,99.841705</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:43</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>105.053856,104.975288,104.873596,104.736885,104.731079,104.710564</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>105.165123,105.192719,104.963058,104.939400,105.063217,104.972580</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>102.450516,101.840797,101.393471,100.872795,100.723534,100.438400</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>103.447357,103.153267,102.723251,102.442749,102.203964,102.137001</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +3837,44 @@
       </c>
       <c r="F90" t="n">
         <v>104.710563659668</v>
+      </c>
+      <c r="G90" t="n">
+        <v>104.7300033569336</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.01943969726559658</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.0185617269574064</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.7577321952739923</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:52</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" t="n">
+        <v>104.6808624267578</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9315,6 +9353,24 @@
           <t>105.053856,104.975288,104.873596,104.736885,104.731079,104.710564</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>106.470001,103.650002,103.400002,104.320000,104.830002,104.730003</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1.416145,1.325286,1.473594,0.416885,0.098923,0.019439</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1.330088,1.278617,1.425140,0.399622,0.094365,0.018561</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.7577321952739923</v>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>105.165123,105.192719,104.963058,104.939400,105.063217,104.972580</t>
@@ -9328,6 +9384,49 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>103.447357,103.153267,102.723251,102.442749,102.203964,102.137001</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:52</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>104.645584,104.729469,104.647987,104.615936,104.723938,104.680862</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>104.721909,104.747002,104.663033,104.729485,104.947899,104.806343</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>101.921837,101.515015,101.148003,100.829979,100.794579,100.455376</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>103.047379,102.833611,102.485123,102.328117,102.361664,102.210518</t>
         </is>
       </c>
     </row>
